--- a/assets/jstyle-cup-2026-entry.xlsx
+++ b/assets/jstyle-cup-2026-entry.xlsx
@@ -2793,11 +2793,13 @@
     </row>
     <row r="12" spans="1:40" ht="33" customHeight="1">
       <c r="B12" s="65"/>
-      <c r="C12" s="70" t="s">
-        <v>34</v>
+      <c r="C12" s="70" t="inlineStr">
+        <is>
+          <t>小学２年生以下</t>
+        </is>
       </c>
       <c r="D12" s="53">
-        <f>COUNTA($M$16:$M$25)</f>
+        <f>COUNTA($M$49:$M$58)</f>
         <v>0</v>
       </c>
       <c r="E12" s="10" t="s">
@@ -2815,11 +2817,13 @@
       <c r="B13" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="71" t="s">
-        <v>36</v>
+      <c r="C13" s="71" t="inlineStr">
+        <is>
+          <t>小学６年生以下　男子</t>
+        </is>
       </c>
       <c r="D13" s="55">
-        <f>COUNTA($S$16:$S$30)</f>
+        <f>COUNTA($Y$16:$Y$30)</f>
         <v>0</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -2841,11 +2845,13 @@
       <c r="B14" s="66">
         <v>46382</v>
       </c>
-      <c r="C14" s="71" t="s">
-        <v>37</v>
+      <c r="C14" s="71" t="inlineStr">
+        <is>
+          <t>小学６年生以下　女子</t>
+        </is>
       </c>
       <c r="D14" s="55">
-        <f>COUNTA($S$49:$S$63)</f>
+        <f>COUNTA($Y$49:$Y$63)</f>
         <v>0</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -2895,11 +2901,13 @@
     </row>
     <row r="15" spans="1:40" ht="27">
       <c r="B15" s="67"/>
-      <c r="C15" s="71" t="s">
-        <v>41</v>
+      <c r="C15" s="71" t="inlineStr">
+        <is>
+          <t>高校・一般の部　男子</t>
+        </is>
       </c>
       <c r="D15" s="55">
-        <f>COUNTA($AE$16:$AE$45)</f>
+        <f>COUNTA($AL$16:$AL$45)</f>
         <v>0</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -2981,11 +2989,13 @@
     </row>
     <row r="16" spans="1:40" ht="28" thickBot="1">
       <c r="B16" s="67"/>
-      <c r="C16" s="72" t="s">
-        <v>40</v>
+      <c r="C16" s="72" t="inlineStr">
+        <is>
+          <t>高校・一般の部　女子</t>
+        </is>
       </c>
       <c r="D16" s="54">
-        <f>COUNTA($AE$49:$AE$78)</f>
+        <f>COUNTA($AL$49:$AL$78)</f>
         <v>0</v>
       </c>
       <c r="E16" s="36" t="s">
@@ -3050,11 +3060,13 @@
     </row>
     <row r="17" spans="2:40" ht="27">
       <c r="B17" s="65"/>
-      <c r="C17" s="70" t="s">
-        <v>35</v>
+      <c r="C17" s="70" t="inlineStr">
+        <is>
+          <t>小学１年生以下</t>
+        </is>
       </c>
       <c r="D17" s="53">
-        <f>COUNTA($M$49:$M$58)</f>
+        <f>COUNTA($M$16:$M$25)</f>
         <v>0</v>
       </c>
       <c r="E17" s="10" t="s">
@@ -3118,11 +3130,13 @@
       <c r="B18" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="71" t="s">
-        <v>38</v>
+      <c r="C18" s="71" t="inlineStr">
+        <is>
+          <t>小学４年生以下　男子</t>
+        </is>
       </c>
       <c r="D18" s="55">
-        <f>COUNTA($Y$16:$Y$30)</f>
+        <f>COUNTA($S$16:$S$30)</f>
         <v>0</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -3189,11 +3203,13 @@
       <c r="B19" s="66">
         <v>46383</v>
       </c>
-      <c r="C19" s="71" t="s">
-        <v>39</v>
+      <c r="C19" s="71" t="inlineStr">
+        <is>
+          <t>小学４年生以下　女子</t>
+        </is>
       </c>
       <c r="D19" s="55">
-        <f>COUNTA($Y$49:$Y$63)</f>
+        <f>COUNTA($S$49:$S$63)</f>
         <v>0</v>
       </c>
       <c r="E19" s="11" t="s">
@@ -3260,11 +3276,13 @@
     </row>
     <row r="20" spans="2:40" ht="27">
       <c r="B20" s="68"/>
-      <c r="C20" s="71" t="s">
-        <v>53</v>
+      <c r="C20" s="71" t="inlineStr">
+        <is>
+          <t>中学３年生以下　男子</t>
+        </is>
       </c>
       <c r="D20" s="55">
-        <f>COUNTA($AL$16:$AL$45)</f>
+        <f>COUNTA($AE$16:$AE$45)</f>
         <v>0</v>
       </c>
       <c r="E20" s="11" t="s">
@@ -3329,11 +3347,13 @@
     </row>
     <row r="21" spans="2:40" ht="28" thickBot="1">
       <c r="B21" s="69"/>
-      <c r="C21" s="72" t="s">
-        <v>54</v>
+      <c r="C21" s="72" t="inlineStr">
+        <is>
+          <t>中学３年生以下　女子</t>
+        </is>
       </c>
       <c r="D21" s="54">
-        <f>COUNTA($AL$49:$AL$78)</f>
+        <f>COUNTA($AE$49:$AE$78)</f>
         <v>0</v>
       </c>
       <c r="E21" s="36" t="s">
